--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-017_休暇付与_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-017_休暇付与_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="13496925"/>
+    <ext cx="8572500" cy="13696950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-017 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-017 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="124" customHeight="1">
+    <row r="3" ht="199" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2526,7 +2526,9 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：E-013 の文言を「付与は既に登録されています。」に統一し UNIQUE 制約 uq_leave_balances_1 違反も E-013 に変換、通知を notify 4引数・type=LEAVE_GRANTED・requestId=null で保存、notifications の INSERT を SQL 欄に追記、adjust の E-003 を 400 に統一、validateGrantedOn の範囲外を E-014 に統一、statutoryDays(long) / buildGrantMessage / buildAdjustMessage を package-private 化、listGrants を付与回数基準（regularGrantCount）に変更、updated_at をトリガ自動更新に変更</t>
+          <t>・確定設計変更 D1〜D10 を反映：E-013 の文言を「付与は既に登録されています。」に統一し UNIQUE 制約 uq_leave_balances_1 違反も E-013 に変換、通知を notify 4引数・type=LEAVE_GRANTED・requestId=null で保存、notifications の INSERT を SQL 欄に追記、adjust の E-003 を 400 に統一、validateGrantedOn の範囲外を E-014 に統一、statutoryDays(long) / buildGrantMessage / buildAdjustMessage を package-private 化、listGrants を付与回数基準（regularGrantCount）に変更、updated_at をトリガ自動更新に変更
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・LeaveBalanceService#grant の日数は setScale(1, RoundingMode.HALF_UP)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -4824,7 +4826,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>grantedDays: 0.1〜99.9・小数第1位まで。grantedOn: 入社日 ≤ 付与日 ≤ 本日(JST)、かつ 付与日+2年 ≧ 本日(JST)（失効日当日までは有効）</t>
+          <t>grantedDays: 0.1〜99.9・小数第1位まで。grantedOn: 入社日 ≤ 付与日 ≤ 本日(clock)、かつ 付与日+2年 ≧ 本日(clock)（失効日当日までは有効）</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -5242,7 +5244,7 @@
         <is>
           <t>@PostMapping
 @ResponseStatus(HttpStatus.CREATED)
-public LeaveGrantResponse create(@Valid @RequestBody LeaveGrantCreateRequest request, @AuthenticationPrincipal Jwt jwt)</t>
+public LeaveGrantResponse create(@Valid @RequestBody LeaveGrantCreateRequest request, Authentication auth)</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -5325,17 +5327,17 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>@AuthenticationPrincipal。sub = ログイン管理者の users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -5385,7 +5387,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Long adminId = Long.valueOf(jwt.getSubject());
+          <t>Long adminId = Long.valueOf(auth.getName());
 return leaveBalanceService.grantManually(request, adminId);</t>
         </is>
       </c>
@@ -5454,7 +5456,7 @@
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="10" t="n"/>
     </row>
-    <row r="32" ht="49" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -5463,7 +5465,7 @@
       <c r="B32" s="12" t="inlineStr">
         <is>
           <t>@PutMapping("/{id}")
-public LeaveGrantResponse adjust(@PathVariable Long id, @Valid @RequestBody LeaveGrantAdjustRequest request, @AuthenticationPrincipal Jwt jwt)</t>
+public LeaveGrantResponse adjust(@PathVariable Long id, @Valid @RequestBody LeaveGrantAdjustRequest request, Authentication auth)</t>
         </is>
       </c>
       <c r="C32" s="9" t="n"/>
@@ -5566,17 +5568,17 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>管理者の users.id（sub）</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
@@ -5624,7 +5626,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Long adminId = Long.valueOf(jwt.getSubject());
+          <t>Long adminId = Long.valueOf(auth.getName());
 return leaveBalanceService.adjust(id, request, adminId);</t>
         </is>
       </c>
